--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_44.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3623835.993052128</v>
+        <v>3624939.793592266</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13607016.77721224</v>
+        <v>13607016.77721222</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13607016.77721224</v>
+        <v>13607016.77721222</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133313.3644572102</v>
+        <v>133313.3644571987</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133313.3644572102</v>
+        <v>133313.3644571987</v>
       </c>
     </row>
     <row r="11">
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.347322035759015</v>
+        <v>3.347322035758213</v>
       </c>
       <c r="H2" t="n">
-        <v>3.810231567849018</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.798687867828012</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964805</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -778,25 +778,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716246</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>374</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796834</v>
+        <v>340.5604285731656</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>202.2183933449087</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -848,10 +848,10 @@
         <v>91.79905402550071</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651275</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970477</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P4" t="n">
         <v>265.2018645413922</v>
@@ -903,10 +903,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>6.688316575838376</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>5.146009903586449</v>
       </c>
       <c r="H5" t="n">
         <v>3.81023156784903</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>217.3561651149423</v>
       </c>
       <c r="T6" t="n">
-        <v>157.7866771673788</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
         <v>0.1959257979225981</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1146,10 +1146,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>22.51305487478915</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1267,16 +1267,16 @@
         <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>119.1163727396089</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1383,10 +1383,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H11" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I11" t="n">
-        <v>1.388898923102739</v>
+        <v>1.388898923102767</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T11" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
@@ -1456,13 +1456,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H12" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,31 +1489,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.532287858417</v>
+        <v>372.2590055347301</v>
       </c>
       <c r="S12" t="n">
         <v>131.5805093985736</v>
       </c>
       <c r="T12" t="n">
-        <v>81.32333125524967</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>214.6083052387684</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M13" t="n">
         <v>100.6963655009106</v>
@@ -1574,7 +1574,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S13" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1693,13 +1693,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>134.3818081312579</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>3.986705686348103</v>
       </c>
       <c r="H15" t="n">
-        <v>324.89733246944</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>179.532287858417</v>
@@ -1738,7 +1738,7 @@
         <v>81.32333125524968</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16083145829998</v>
+        <v>271.8875491346133</v>
       </c>
       <c r="V15" t="n">
         <v>414.5106671915202</v>
@@ -1750,7 +1750,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1857,10 +1857,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H17" t="n">
-        <v>73.98875863165527</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.388898923102767</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>3.986705686348103</v>
@@ -1984,10 +1984,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>291.5894571217008</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>271.1181104424473</v>
       </c>
     </row>
     <row r="19">
@@ -2094,10 +2094,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H20" t="n">
-        <v>72.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I20" t="n">
-        <v>1.388898923102767</v>
+        <v>1.388898923102739</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.7853537319712</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T20" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U20" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V20" t="n">
         <v>308.8510241668239</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>211.36296001419</v>
       </c>
       <c r="G21" t="n">
-        <v>3.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H21" t="n">
-        <v>3.897332469440016</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2209,22 +2209,22 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T21" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>271.1181104424475</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M22" t="n">
         <v>100.6963655009106</v>
@@ -2285,7 +2285,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S22" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.388898923102697</v>
       </c>
       <c r="S23" t="n">
-        <v>143.1742526550738</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T23" t="n">
         <v>259.5162852461518</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>232.8266301218324</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.986705686348103</v>
@@ -2455,13 +2455,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>304.0998605861415</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2553,7 +2553,7 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>133.7442771660967</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>89.33915573984979</v>
@@ -2568,7 +2568,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H26" t="n">
-        <v>72.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>141.7853537319712</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T26" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2619,7 +2619,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>190.3174326828064</v>
+        <v>195.5871316059091</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>142.6832526910834</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>211.3629600141899</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H27" t="n">
-        <v>3.897332469440016</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>179.532287858417</v>
@@ -2683,10 +2683,10 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T27" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M28" t="n">
         <v>100.6963655009106</v>
@@ -2759,7 +2759,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S28" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H29" t="n">
-        <v>77.86955863165528</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,16 +2835,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S29" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T29" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U29" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V29" t="n">
         <v>308.8510241668239</v>
@@ -2869,7 +2869,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>232.8266301218324</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -2878,13 +2878,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H30" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T30" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2935,7 +2935,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>78.39139276613435</v>
+        <v>271.1181104424473</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M31" t="n">
         <v>100.6963655009106</v>
@@ -2996,7 +2996,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S31" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H32" t="n">
-        <v>77.86955863165528</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>141.7853537319712</v>
+        <v>147.0550526550739</v>
       </c>
       <c r="T32" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>256.2832743226397</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>214.3988148982259</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H33" t="n">
-        <v>3.897332469440016</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3157,16 +3157,16 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T33" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>98.86273944538755</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M34" t="n">
         <v>100.6963655009106</v>
@@ -3233,7 +3233,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S34" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,10 +3276,10 @@
         <v>60.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>58.35033711113681</v>
+        <v>58.35033711113682</v>
       </c>
       <c r="H35" t="n">
-        <v>49.59985970855251</v>
+        <v>49.59985970855254</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>118.7853537319712</v>
+        <v>118.7853537319711</v>
       </c>
       <c r="T35" t="n">
         <v>236.5162852461518</v>
       </c>
       <c r="U35" t="n">
-        <v>305.1087337345404</v>
+        <v>305.1087337345403</v>
       </c>
       <c r="V35" t="n">
         <v>285.8510241668239</v>
@@ -3330,7 +3330,7 @@
         <v>248.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>160.8383316059094</v>
+        <v>160.8383316059245</v>
       </c>
     </row>
     <row r="36">
@@ -3346,13 +3346,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>84.8567822895938</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>86.61075583210138</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3394,22 +3394,22 @@
         <v>108.5805093985736</v>
       </c>
       <c r="T36" t="n">
-        <v>58.32333125524968</v>
+        <v>58.32333125524966</v>
       </c>
       <c r="U36" t="n">
-        <v>56.16083145829998</v>
+        <v>56.16083145829995</v>
       </c>
       <c r="V36" t="n">
-        <v>70.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>88.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>75.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>55.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>77.69636550091059</v>
+        <v>77.69636550091056</v>
       </c>
       <c r="N37" t="n">
         <v>130.602288386439</v>
@@ -3470,7 +3470,7 @@
         <v>354.2234394565609</v>
       </c>
       <c r="S37" t="n">
-        <v>7.374299374986606</v>
+        <v>7.374299374986586</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>112.3062526550743</v>
+        <v>112.3062526550887</v>
       </c>
       <c r="T38" t="n">
         <v>236.5162852461518</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>17.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9867056863481</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>324.89733246944</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>43.38180813125796</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R39" t="n">
-        <v>156.532287858417</v>
+        <v>161.7981341454633</v>
       </c>
       <c r="S39" t="n">
         <v>108.5805093985736</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>160.9993129555745</v>
+        <v>114.9449869413753</v>
       </c>
       <c r="C41" t="n">
-        <v>128.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>89.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>26.1660219906393</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.35033711113681</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>72.59985970855251</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>141.7853537319712</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T41" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U41" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V41" t="n">
         <v>308.8510241668239</v>
@@ -3801,7 +3801,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>190.3174326828064</v>
@@ -3817,10 +3817,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
@@ -3829,10 +3829,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.986705686348103</v>
+        <v>196.7134233626614</v>
       </c>
       <c r="H42" t="n">
-        <v>3.897332469440016</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T42" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U42" t="n">
-        <v>271.8875491346129</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V42" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
         <v>432.3731429098285</v>
@@ -3883,7 +3883,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M43" t="n">
         <v>100.6963655009106</v>
@@ -3944,7 +3944,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S43" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3975,22 +3975,22 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>128.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>89.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>26.16602199063924</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>83.88962870801186</v>
+        <v>37.83530269381269</v>
       </c>
       <c r="G44" t="n">
-        <v>81.35033711113681</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>72.59985970855254</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T44" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U44" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V44" t="n">
         <v>308.8510241668239</v>
@@ -4038,7 +4038,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>190.3174326828064</v>
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.55655664632661</v>
+        <v>256.2832743226397</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>211.3629600141902</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H45" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>500.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S45" t="n">
         <v>131.5805093985736</v>
       </c>
       <c r="T45" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M46" t="n">
         <v>100.6963655009106</v>
@@ -4181,7 +4181,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S46" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.9141473750831</v>
+        <v>106.9141473750823</v>
       </c>
       <c r="C2" t="n">
-        <v>56.93982591751346</v>
+        <v>56.93982591751266</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426109953</v>
+        <v>46.49623426109873</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183827</v>
+        <v>42.08887102183748</v>
       </c>
       <c r="F2" t="n">
-        <v>37.1498521248566</v>
+        <v>37.1498521248558</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540305</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,52 +4321,52 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K2" t="n">
         <v>400.18</v>
       </c>
-      <c r="K2" t="n">
-        <v>697.3881081337421</v>
-      </c>
       <c r="L2" t="n">
-        <v>1067.648108133742</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>1140.7</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>1140.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.18314356785</v>
       </c>
       <c r="S2" t="n">
         <v>1407.815317606416</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178447</v>
+        <v>1221.067250178446</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698509</v>
+        <v>969.3617021698501</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861904</v>
+        <v>737.1889504861896</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165464</v>
+        <v>496.4076616165456</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138517</v>
+        <v>302.1835874138509</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190977</v>
+        <v>189.7417362190969</v>
       </c>
     </row>
     <row r="3">
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>983.2202161902781</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>978.7015854197762</v>
+        <v>807.3386312408292</v>
       </c>
       <c r="U3" t="n">
-        <v>600.9238076419983</v>
+        <v>807.1407263944427</v>
       </c>
       <c r="V3" t="n">
-        <v>586.2665680546042</v>
+        <v>792.4834868070486</v>
       </c>
       <c r="W3" t="n">
-        <v>382.0055646759086</v>
+        <v>759.7833424536865</v>
       </c>
       <c r="X3" t="n">
-        <v>361.9421914987495</v>
+        <v>739.7199692765273</v>
       </c>
       <c r="Y3" t="n">
-        <v>361.9421914987495</v>
+        <v>739.7199692765273</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>196.3456815683466</v>
+        <v>29.92</v>
       </c>
       <c r="D4" t="n">
-        <v>309.6648256933467</v>
+        <v>91.43988839788217</v>
       </c>
       <c r="E4" t="n">
-        <v>427.4937299047597</v>
+        <v>209.2687926092952</v>
       </c>
       <c r="F4" t="n">
-        <v>551.8547024966953</v>
+        <v>333.6297652012307</v>
       </c>
       <c r="G4" t="n">
-        <v>705.4433634655477</v>
+        <v>487.2184261700831</v>
       </c>
       <c r="H4" t="n">
-        <v>876.5789394446174</v>
+        <v>658.3540021491528</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401252</v>
+        <v>884.9629768229406</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240125</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4494,10 +4494,10 @@
         <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660643</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121328</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
         <v>351.4672397226398</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="V4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="W4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="X4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="5">
@@ -4546,7 +4546,7 @@
         <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
         <v>33.76871875540306</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>921.1259505599992</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="C6" t="n">
-        <v>921.1259505599992</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="D6" t="n">
-        <v>921.1259505599992</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="E6" t="n">
-        <v>574.9925190227137</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="F6" t="n">
-        <v>574.9925190227137</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="G6" t="n">
-        <v>574.9925190227137</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1138.232342402307</v>
       </c>
       <c r="T6" t="n">
-        <v>988.744612524301</v>
+        <v>1133.713711631805</v>
       </c>
       <c r="U6" t="n">
-        <v>988.5467076779146</v>
+        <v>1133.515806785418</v>
       </c>
       <c r="V6" t="n">
-        <v>973.8894680905205</v>
+        <v>1118.858567198024</v>
       </c>
       <c r="W6" t="n">
-        <v>941.1893237371584</v>
+        <v>741.0807894202462</v>
       </c>
       <c r="X6" t="n">
-        <v>921.1259505599992</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="Y6" t="n">
-        <v>921.1259505599992</v>
+        <v>363.3030116424684</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="C7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="D7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="E7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="F7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="G7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="H7" t="n">
-        <v>881.2025562401257</v>
+        <v>658.3540021491528</v>
       </c>
       <c r="I7" t="n">
-        <v>881.2025562401257</v>
+        <v>884.9629768229406</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4752,16 +4752,16 @@
         <v>505.7585226289696</v>
       </c>
       <c r="V7" t="n">
-        <v>704.5799155149155</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="W7" t="n">
-        <v>876.4708337745928</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="X7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="Y7" t="n">
-        <v>881.2025562401257</v>
+        <v>505.7585226289696</v>
       </c>
     </row>
     <row r="8">
@@ -4789,25 +4789,25 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K8" t="n">
         <v>400.18</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>770.4399999999999</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1067.648108133742</v>
       </c>
       <c r="M8" t="n">
         <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O8" t="n">
         <v>1437.908108133742</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>381.3722089875785</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C9" t="n">
-        <v>381.3722089875785</v>
+        <v>1053.247342307264</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>701.7951333196861</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>701.7951333196861</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V9" t="n">
-        <v>1169.627908896496</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W9" t="n">
-        <v>1136.927764543134</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X9" t="n">
-        <v>759.1499867653563</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y9" t="n">
-        <v>381.3722089875785</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1021.390865612444</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="C10" t="n">
-        <v>1147.39287143088</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="D10" t="n">
-        <v>1260.71201555588</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="E10" t="n">
-        <v>1378.540919767293</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="F10" t="n">
-        <v>1386.743548464727</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U10" t="n">
-        <v>276.481125097303</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V10" t="n">
-        <v>475.302517983249</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W10" t="n">
-        <v>647.1934362429264</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="X10" t="n">
-        <v>798.2242272671199</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="Y10" t="n">
-        <v>909.6335279461522</v>
+        <v>876.4708337745928</v>
       </c>
     </row>
     <row r="11">
@@ -5026,22 +5026,22 @@
         <v>126.6561198299548</v>
       </c>
       <c r="H11" t="n">
-        <v>53.32292820515428</v>
+        <v>53.32292820515431</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>135.4535720585666</v>
+        <v>561.4552612788618</v>
       </c>
       <c r="K11" t="n">
-        <v>725.9802989115907</v>
+        <v>1203.965261278862</v>
       </c>
       <c r="L11" t="n">
-        <v>945.8005953940028</v>
+        <v>1588.310595394003</v>
       </c>
       <c r="M11" t="n">
-        <v>1588.310595394003</v>
+        <v>2230.820595394003</v>
       </c>
       <c r="N11" t="n">
         <v>2230.820595394003</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>492.556340463434</v>
+        <v>168.3139162210097</v>
       </c>
       <c r="C12" t="n">
-        <v>452.0513783972528</v>
+        <v>127.8089541548285</v>
       </c>
       <c r="D12" t="n">
-        <v>424.8415936520987</v>
+        <v>100.5991694096744</v>
       </c>
       <c r="E12" t="n">
-        <v>402.9505863572374</v>
+        <v>78.70816211481312</v>
       </c>
       <c r="F12" t="n">
-        <v>59.88367490483647</v>
+        <v>59.88367490483648</v>
       </c>
       <c r="G12" t="n">
-        <v>55.85669946408081</v>
+        <v>55.85669946408083</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2262.271670368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2184.512931092847</v>
+        <v>2262.271670368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2003.167185781314</v>
+        <v>1886.252472858708</v>
       </c>
       <c r="S12" t="n">
-        <v>1870.25758032821</v>
+        <v>1753.342867405603</v>
       </c>
       <c r="T12" t="n">
-        <v>1788.112801282503</v>
+        <v>1346.955664117472</v>
       </c>
       <c r="U12" t="n">
-        <v>1708.152365466038</v>
+        <v>1266.995228301007</v>
       </c>
       <c r="V12" t="n">
-        <v>1613.697146080664</v>
+        <v>1172.540008915633</v>
       </c>
       <c r="W12" t="n">
-        <v>1501.199021929322</v>
+        <v>735.7994605218669</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.422956031576</v>
+        <v>311.6956833043036</v>
       </c>
       <c r="Y12" t="n">
-        <v>880.9973067728548</v>
+        <v>232.5124582880063</v>
       </c>
     </row>
     <row r="13">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6904483778065</v>
       </c>
       <c r="C13" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4824541962423</v>
       </c>
       <c r="D13" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5915983212424</v>
       </c>
       <c r="E13" t="n">
         <v>798.1069956511426</v>
@@ -5211,10 +5211,10 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.6348877086339</v>
+        <v>463.6348877086338</v>
       </c>
       <c r="R13" t="n">
-        <v>82.60111047978444</v>
+        <v>82.60111047978445</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5226,16 +5226,16 @@
         <v>332.8307078626652</v>
       </c>
       <c r="V13" t="n">
-        <v>442.3385938670984</v>
+        <v>453.4421007486112</v>
       </c>
       <c r="W13" t="n">
-        <v>536.0195121267758</v>
+        <v>547.1230190082886</v>
       </c>
       <c r="X13" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y13" t="n">
-        <v>642.0396038300016</v>
+        <v>653.1431107115144</v>
       </c>
     </row>
     <row r="14">
@@ -5272,16 +5272,16 @@
         <v>135.4535720585666</v>
       </c>
       <c r="K14" t="n">
-        <v>312.6439213047977</v>
+        <v>777.9635720585666</v>
       </c>
       <c r="L14" t="n">
-        <v>945.8005953940028</v>
+        <v>1110.954106525702</v>
       </c>
       <c r="M14" t="n">
-        <v>1588.310595394003</v>
+        <v>1110.954106525702</v>
       </c>
       <c r="N14" t="n">
-        <v>2230.820595394003</v>
+        <v>1753.464106525702</v>
       </c>
       <c r="O14" t="n">
         <v>2395.974106525702</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>609.4710533860409</v>
+        <v>168.3139162210097</v>
       </c>
       <c r="C15" t="n">
-        <v>568.9660913198599</v>
+        <v>127.8089541548285</v>
       </c>
       <c r="D15" t="n">
-        <v>541.7563065747057</v>
+        <v>100.5991694096744</v>
       </c>
       <c r="E15" t="n">
-        <v>519.8652992798445</v>
+        <v>78.70816211481312</v>
       </c>
       <c r="F15" t="n">
-        <v>384.1260991472608</v>
+        <v>59.88367490483648</v>
       </c>
       <c r="G15" t="n">
-        <v>380.0991237065051</v>
+        <v>55.85669946408083</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5369,31 +5369,31 @@
         <v>2262.271670368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2184.512931092847</v>
+        <v>2262.271670368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2003.167185781314</v>
+        <v>2080.925925057003</v>
       </c>
       <c r="S15" t="n">
-        <v>1870.25758032821</v>
+        <v>1948.016319603899</v>
       </c>
       <c r="T15" t="n">
-        <v>1788.112801282503</v>
+        <v>1865.871540558192</v>
       </c>
       <c r="U15" t="n">
-        <v>1708.152365466038</v>
+        <v>1591.237652543431</v>
       </c>
       <c r="V15" t="n">
-        <v>1289.45472183824</v>
+        <v>1172.540008915633</v>
       </c>
       <c r="W15" t="n">
-        <v>1176.956597686898</v>
+        <v>1060.041884764291</v>
       </c>
       <c r="X15" t="n">
-        <v>1077.095244711759</v>
+        <v>960.180531789152</v>
       </c>
       <c r="Y15" t="n">
-        <v>997.9120196954617</v>
+        <v>556.7548825304305</v>
       </c>
     </row>
     <row r="16">
@@ -5469,7 +5469,7 @@
         <v>547.1230190082886</v>
       </c>
       <c r="X16" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y16" t="n">
         <v>642.0396038300016</v>
@@ -5500,7 +5500,7 @@
         <v>126.6561198299548</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>53.32292820515431</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>492.5563404634339</v>
+        <v>816.7987647058583</v>
       </c>
       <c r="C18" t="n">
-        <v>127.8089541548285</v>
+        <v>452.0513783972528</v>
       </c>
       <c r="D18" t="n">
-        <v>100.5991694096744</v>
+        <v>424.8415936520987</v>
       </c>
       <c r="E18" t="n">
-        <v>78.70816211481312</v>
+        <v>402.9505863572374</v>
       </c>
       <c r="F18" t="n">
         <v>59.88367490483648</v>
@@ -5627,10 +5627,10 @@
         <v>1578.957761205011</v>
       </c>
       <c r="X18" t="n">
-        <v>1284.422956031576</v>
+        <v>1479.096408229872</v>
       </c>
       <c r="Y18" t="n">
-        <v>880.9973067728547</v>
+        <v>1205.239731015279</v>
       </c>
     </row>
     <row r="19">
@@ -5737,7 +5737,7 @@
         <v>126.6561198299548</v>
       </c>
       <c r="H20" t="n">
-        <v>53.32292820515431</v>
+        <v>53.32292820515428</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
@@ -5746,22 +5746,22 @@
         <v>561.4552612788618</v>
       </c>
       <c r="K20" t="n">
-        <v>999.286970190582</v>
+        <v>1203.965261278862</v>
       </c>
       <c r="L20" t="n">
-        <v>1641.796970190582</v>
+        <v>1846.475261278862</v>
       </c>
       <c r="M20" t="n">
-        <v>1641.796970190582</v>
+        <v>2230.820595394003</v>
       </c>
       <c r="N20" t="n">
-        <v>1641.796970190582</v>
+        <v>2230.820595394003</v>
       </c>
       <c r="O20" t="n">
-        <v>1806.950481322281</v>
+        <v>2395.974106525702</v>
       </c>
       <c r="P20" t="n">
-        <v>2006.976374796579</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.3139162210097</v>
+        <v>1335.714641146579</v>
       </c>
       <c r="C21" t="n">
-        <v>127.8089541548285</v>
+        <v>970.9672548379731</v>
       </c>
       <c r="D21" t="n">
-        <v>100.5991694096744</v>
+        <v>619.5150458503947</v>
       </c>
       <c r="E21" t="n">
-        <v>78.70816211481312</v>
+        <v>273.3816143131092</v>
       </c>
       <c r="F21" t="n">
-        <v>59.88367490483648</v>
+        <v>59.88367490483647</v>
       </c>
       <c r="G21" t="n">
-        <v>55.85669946408083</v>
+        <v>55.85669946408081</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5858,16 +5858,16 @@
         <v>1785.911104741727</v>
       </c>
       <c r="V21" t="n">
-        <v>1367.213461113929</v>
+        <v>1691.455885356353</v>
       </c>
       <c r="W21" t="n">
-        <v>930.4729127201629</v>
+        <v>1578.957761205011</v>
       </c>
       <c r="X21" t="n">
-        <v>506.3691355025996</v>
+        <v>1479.096408229872</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.5124582880063</v>
+        <v>1399.913183213575</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6904483778065</v>
+        <v>675.5869414962938</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4824541962423</v>
+        <v>723.3789473147295</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5915983212424</v>
+        <v>758.4880914397296</v>
       </c>
       <c r="E22" t="n">
-        <v>809.2105025326554</v>
+        <v>798.1069956511426</v>
       </c>
       <c r="F22" t="n">
-        <v>855.3614751245908</v>
+        <v>844.257968243078</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1828770770499</v>
+        <v>920.0793701955371</v>
       </c>
       <c r="H22" t="n">
-        <v>1028.044822892185</v>
+        <v>1016.941316010672</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.758226418432</v>
+        <v>1178.654719536919</v>
       </c>
       <c r="J22" t="n">
-        <v>1516.807876906949</v>
+        <v>1505.704370025436</v>
       </c>
       <c r="K22" t="n">
         <v>1610.453394126239</v>
@@ -5922,10 +5922,10 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.6348877086338</v>
+        <v>463.6348877086339</v>
       </c>
       <c r="R22" t="n">
-        <v>82.60111047978445</v>
+        <v>82.60111047978444</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5983,13 +5983,13 @@
         <v>561.4552612788618</v>
       </c>
       <c r="K23" t="n">
-        <v>738.645610525093</v>
+        <v>999.286970190582</v>
       </c>
       <c r="L23" t="n">
-        <v>999.286970190582</v>
+        <v>1641.796970190582</v>
       </c>
       <c r="M23" t="n">
-        <v>999.286970190582</v>
+        <v>1641.796970190582</v>
       </c>
       <c r="N23" t="n">
         <v>1641.796970190582</v>
@@ -6004,7 +6004,7 @@
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2594.597071794846</v>
       </c>
       <c r="S23" t="n">
         <v>2451.379542772653</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.3139162210097</v>
+        <v>1335.714641146579</v>
       </c>
       <c r="C24" t="n">
-        <v>127.8089541548285</v>
+        <v>1100.536226882101</v>
       </c>
       <c r="D24" t="n">
-        <v>100.5991694096744</v>
+        <v>749.084017894523</v>
       </c>
       <c r="E24" t="n">
-        <v>78.70816211481312</v>
+        <v>402.9505863572374</v>
       </c>
       <c r="F24" t="n">
         <v>59.88367490483648</v>
@@ -6098,13 +6098,13 @@
         <v>1691.455885356353</v>
       </c>
       <c r="W24" t="n">
-        <v>1384.284309006715</v>
+        <v>1578.957761205011</v>
       </c>
       <c r="X24" t="n">
-        <v>960.180531789152</v>
+        <v>1479.096408229872</v>
       </c>
       <c r="Y24" t="n">
-        <v>556.7548825304305</v>
+        <v>1399.913183213575</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6904483778065</v>
       </c>
       <c r="C25" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4824541962423</v>
       </c>
       <c r="D25" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5915983212424</v>
       </c>
       <c r="E25" t="n">
-        <v>798.1069956511426</v>
+        <v>809.2105025326554</v>
       </c>
       <c r="F25" t="n">
-        <v>844.257968243078</v>
+        <v>855.3614751245908</v>
       </c>
       <c r="G25" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1828770770499</v>
       </c>
       <c r="H25" t="n">
-        <v>1016.941316010672</v>
+        <v>1028.044822892185</v>
       </c>
       <c r="I25" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.758226418432</v>
       </c>
       <c r="J25" t="n">
         <v>1505.704370025436</v>
@@ -6168,22 +6168,22 @@
         <v>51.92</v>
       </c>
       <c r="T25" t="n">
-        <v>153.3519263756527</v>
+        <v>164.4554332571655</v>
       </c>
       <c r="U25" t="n">
-        <v>321.7272009811524</v>
+        <v>332.8307078626652</v>
       </c>
       <c r="V25" t="n">
-        <v>442.3385938670984</v>
+        <v>453.4421007486112</v>
       </c>
       <c r="W25" t="n">
-        <v>536.0195121267758</v>
+        <v>547.1230190082886</v>
       </c>
       <c r="X25" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y25" t="n">
-        <v>642.0396038300016</v>
+        <v>653.1431107115144</v>
       </c>
     </row>
     <row r="26">
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>601.7843919601175</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C26" t="n">
         <v>466.6891624994138</v>
       </c>
       <c r="D26" t="n">
-        <v>376.44759104502</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E26" t="n">
         <v>292.242248007779</v>
@@ -6217,22 +6217,22 @@
         <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>561.5352612788618</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K26" t="n">
-        <v>1205.035261278862</v>
+        <v>779.0335720585665</v>
       </c>
       <c r="L26" t="n">
-        <v>1848.535261278862</v>
+        <v>1422.533572058567</v>
       </c>
       <c r="M26" t="n">
-        <v>2234.820595394003</v>
+        <v>1791.346488868301</v>
       </c>
       <c r="N26" t="n">
-        <v>2234.820595394003</v>
+        <v>1791.346488868301</v>
       </c>
       <c r="O26" t="n">
-        <v>2399.974106525702</v>
+        <v>1956.5</v>
       </c>
       <c r="P26" t="n">
         <v>2600</v>
@@ -6262,7 +6262,7 @@
         <v>956.6497915948457</v>
       </c>
       <c r="Y26" t="n">
-        <v>764.4099606021121</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1258.035901870889</v>
+        <v>1011.552216904154</v>
       </c>
       <c r="C27" t="n">
-        <v>1217.530939804708</v>
+        <v>646.8048305955488</v>
       </c>
       <c r="D27" t="n">
-        <v>1073.406442136947</v>
+        <v>619.5950458503946</v>
       </c>
       <c r="E27" t="n">
-        <v>727.2730105996617</v>
+        <v>273.4616143131091</v>
       </c>
       <c r="F27" t="n">
-        <v>384.2060991472608</v>
+        <v>59.96367490483647</v>
       </c>
       <c r="G27" t="n">
-        <v>55.93669946408082</v>
+        <v>55.93669946408081</v>
       </c>
       <c r="H27" t="n">
         <v>52</v>
@@ -6317,31 +6317,31 @@
         <v>2262.351670368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2184.592931092847</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2003.247185781314</v>
+        <v>2081.005925057003</v>
       </c>
       <c r="S27" t="n">
-        <v>1870.33758032821</v>
+        <v>1948.096319603899</v>
       </c>
       <c r="T27" t="n">
-        <v>1788.192801282503</v>
+        <v>1865.951540558192</v>
       </c>
       <c r="U27" t="n">
-        <v>1708.232365466038</v>
+        <v>1785.991104741727</v>
       </c>
       <c r="V27" t="n">
-        <v>1613.777146080664</v>
+        <v>1691.535885356353</v>
       </c>
       <c r="W27" t="n">
-        <v>1501.279021929322</v>
+        <v>1579.037761205011</v>
       </c>
       <c r="X27" t="n">
-        <v>1401.417668954183</v>
+        <v>1479.176408229872</v>
       </c>
       <c r="Y27" t="n">
-        <v>1322.234443937886</v>
+        <v>1399.993183213575</v>
       </c>
     </row>
     <row r="28">
@@ -6363,7 +6363,7 @@
         <v>809.2905025326555</v>
       </c>
       <c r="F28" t="n">
-        <v>844.337968243078</v>
+        <v>855.441475124591</v>
       </c>
       <c r="G28" t="n">
         <v>920.159370195537</v>
@@ -6396,10 +6396,10 @@
         <v>819.2596012698439</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.7148877086338</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R28" t="n">
-        <v>82.68111047978445</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S28" t="n">
         <v>52</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>601.7843919601175</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C29" t="n">
-        <v>472.0120907045681</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D29" t="n">
-        <v>381.7705192501743</v>
+        <v>376.44759104502</v>
       </c>
       <c r="E29" t="n">
-        <v>297.5651762129333</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F29" t="n">
-        <v>212.8281775179718</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G29" t="n">
-        <v>130.6561198299548</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H29" t="n">
         <v>52</v>
@@ -6454,13 +6454,13 @@
         <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>561.5352612788618</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K29" t="n">
-        <v>1205.035261278862</v>
+        <v>728.0002989115908</v>
       </c>
       <c r="L29" t="n">
-        <v>1591.320595394003</v>
+        <v>947.8205953940028</v>
       </c>
       <c r="M29" t="n">
         <v>1591.320595394003</v>
@@ -6478,28 +6478,28 @@
         <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2600</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S29" t="n">
-        <v>2456.782470977807</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T29" t="n">
-        <v>2194.644809113007</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U29" t="n">
-        <v>1863.221845744784</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V29" t="n">
-        <v>1551.251114263144</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W29" t="n">
-        <v>1230.67184559552</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X29" t="n">
-        <v>956.6497915948457</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y29" t="n">
-        <v>764.4099606021121</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1335.794641146578</v>
+        <v>1141.121188948282</v>
       </c>
       <c r="C30" t="n">
-        <v>1100.616226882101</v>
+        <v>776.373802639677</v>
       </c>
       <c r="D30" t="n">
-        <v>749.1640178945229</v>
+        <v>424.9215936520986</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0305863572374</v>
+        <v>78.7881621148131</v>
       </c>
       <c r="F30" t="n">
-        <v>59.96367490483647</v>
+        <v>59.96367490483648</v>
       </c>
       <c r="G30" t="n">
-        <v>55.93669946408081</v>
+        <v>55.93669946408082</v>
       </c>
       <c r="H30" t="n">
         <v>52</v>
@@ -6578,7 +6578,7 @@
         <v>1479.176408229872</v>
       </c>
       <c r="Y30" t="n">
-        <v>1399.993183213575</v>
+        <v>1205.319731015279</v>
       </c>
     </row>
     <row r="31">
@@ -6597,10 +6597,10 @@
         <v>769.6715983212425</v>
       </c>
       <c r="E31" t="n">
-        <v>798.1869956511425</v>
+        <v>809.2905025326555</v>
       </c>
       <c r="F31" t="n">
-        <v>844.337968243078</v>
+        <v>855.441475124591</v>
       </c>
       <c r="G31" t="n">
         <v>920.159370195537</v>
@@ -6633,10 +6633,10 @@
         <v>819.2596012698439</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.7148877086339</v>
+        <v>463.7148877086338</v>
       </c>
       <c r="R31" t="n">
-        <v>82.68111047978442</v>
+        <v>82.68111047978445</v>
       </c>
       <c r="S31" t="n">
         <v>52</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>601.7843919601175</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C32" t="n">
-        <v>472.0120907045681</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D32" t="n">
-        <v>381.7705192501743</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E32" t="n">
-        <v>297.5651762129333</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F32" t="n">
-        <v>212.8281775179718</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G32" t="n">
-        <v>130.6561198299548</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H32" t="n">
         <v>52</v>
@@ -6694,22 +6694,22 @@
         <v>135.5335720585666</v>
       </c>
       <c r="K32" t="n">
-        <v>779.0335720585665</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L32" t="n">
-        <v>1422.533572058567</v>
+        <v>532.5442177872098</v>
       </c>
       <c r="M32" t="n">
-        <v>1591.320595394003</v>
+        <v>1002.296970190582</v>
       </c>
       <c r="N32" t="n">
-        <v>2234.820595394003</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="O32" t="n">
-        <v>2399.974106525702</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P32" t="n">
-        <v>2600</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q32" t="n">
         <v>2600</v>
@@ -6718,25 +6718,25 @@
         <v>2600</v>
       </c>
       <c r="S32" t="n">
-        <v>2456.782470977807</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T32" t="n">
-        <v>2194.644809113007</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U32" t="n">
-        <v>1863.221845744784</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V32" t="n">
-        <v>1551.251114263144</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W32" t="n">
-        <v>1230.67184559552</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X32" t="n">
-        <v>956.6497915948457</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y32" t="n">
-        <v>764.4099606021121</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1141.121188948282</v>
+        <v>1011.552216904154</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.616226882101</v>
+        <v>646.804830595549</v>
       </c>
       <c r="D33" t="n">
-        <v>749.1640178945229</v>
+        <v>295.3526216079705</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0305863572374</v>
+        <v>78.7881621148131</v>
       </c>
       <c r="F33" t="n">
-        <v>59.96367490483648</v>
+        <v>59.96367490483647</v>
       </c>
       <c r="G33" t="n">
-        <v>55.93669946408082</v>
+        <v>55.93669946408081</v>
       </c>
       <c r="H33" t="n">
         <v>52</v>
@@ -6809,13 +6809,13 @@
         <v>1691.535885356353</v>
       </c>
       <c r="W33" t="n">
-        <v>1579.037761205011</v>
+        <v>1254.795336962587</v>
       </c>
       <c r="X33" t="n">
-        <v>1479.176408229872</v>
+        <v>1154.933983987448</v>
       </c>
       <c r="Y33" t="n">
-        <v>1399.993183213575</v>
+        <v>1075.750758971151</v>
       </c>
     </row>
     <row r="34">
@@ -6870,10 +6870,10 @@
         <v>819.2596012698439</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.7148877086338</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R34" t="n">
-        <v>82.68111047978445</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S34" t="n">
         <v>52</v>
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>450.1875243610237</v>
+        <v>450.1875243610241</v>
       </c>
       <c r="C35" t="n">
-        <v>343.6475463377976</v>
+        <v>343.6475463377979</v>
       </c>
       <c r="D35" t="n">
-        <v>276.6382981157271</v>
+        <v>276.6382981157274</v>
       </c>
       <c r="E35" t="n">
-        <v>215.6652783108093</v>
+        <v>215.6652783108096</v>
       </c>
       <c r="F35" t="n">
-        <v>154.160602848171</v>
+        <v>154.1606028481714</v>
       </c>
       <c r="G35" t="n">
-        <v>95.22086839247729</v>
+        <v>95.22086839247763</v>
       </c>
       <c r="H35" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I35" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J35" t="n">
-        <v>128.6535720585666</v>
+        <v>128.6535720585669</v>
       </c>
       <c r="K35" t="n">
-        <v>554.280298911591</v>
+        <v>305.8439213047981</v>
       </c>
       <c r="L35" t="n">
-        <v>774.1005953940031</v>
+        <v>774.1005953940178</v>
       </c>
       <c r="M35" t="n">
-        <v>1332.460595394003</v>
+        <v>1332.460595394018</v>
       </c>
       <c r="N35" t="n">
-        <v>1890.820595394003</v>
+        <v>1890.820595394018</v>
       </c>
       <c r="O35" t="n">
-        <v>2055.974106525702</v>
+        <v>2055.974106525717</v>
       </c>
       <c r="P35" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="Q35" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="R35" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="S35" t="n">
-        <v>2136.01479421013</v>
+        <v>2136.014794210145</v>
       </c>
       <c r="T35" t="n">
-        <v>1897.109455577654</v>
+        <v>1897.109455577669</v>
       </c>
       <c r="U35" t="n">
-        <v>1588.918815441754</v>
+        <v>1588.91881544177</v>
       </c>
       <c r="V35" t="n">
-        <v>1300.180407192437</v>
+        <v>1300.180407192453</v>
       </c>
       <c r="W35" t="n">
-        <v>1002.833461757137</v>
+        <v>1002.833461757152</v>
       </c>
       <c r="X35" t="n">
-        <v>752.0437309887853</v>
+        <v>752.0437309888008</v>
       </c>
       <c r="Y35" t="n">
-        <v>589.580769770695</v>
+        <v>589.5807697706953</v>
       </c>
     </row>
     <row r="36">
@@ -6983,43 +6983,43 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1538.005550237488</v>
+        <v>495.5813078132459</v>
       </c>
       <c r="C36" t="n">
-        <v>1173.258163928882</v>
+        <v>130.8339215046405</v>
       </c>
       <c r="D36" t="n">
-        <v>821.805954941304</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="E36" t="n">
-        <v>475.6725234040185</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="F36" t="n">
-        <v>132.6056119516176</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="G36" t="n">
-        <v>132.6056119516176</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="H36" t="n">
-        <v>132.6056119516176</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I36" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J36" t="n">
-        <v>239.4912041375631</v>
+        <v>239.4912041375634</v>
       </c>
       <c r="K36" t="n">
-        <v>549.033930609305</v>
+        <v>549.0339306093053</v>
       </c>
       <c r="L36" t="n">
-        <v>982.2096988082787</v>
+        <v>982.2096988082791</v>
       </c>
       <c r="M36" t="n">
         <v>1257.132740551138</v>
       </c>
       <c r="N36" t="n">
-        <v>1584.25362421531</v>
+        <v>1584.253624215311</v>
       </c>
       <c r="O36" t="n">
         <v>2000.622354200916</v>
@@ -7034,25 +7034,25 @@
         <v>2097.358248289327</v>
       </c>
       <c r="S36" t="n">
-        <v>1987.680966068545</v>
+        <v>1987.680966068546</v>
       </c>
       <c r="T36" t="n">
         <v>1928.768510255162</v>
       </c>
       <c r="U36" t="n">
-        <v>1872.04039767102</v>
+        <v>1872.040397671021</v>
       </c>
       <c r="V36" t="n">
-        <v>1800.81750151797</v>
+        <v>1453.342754043223</v>
       </c>
       <c r="W36" t="n">
-        <v>1711.551700598951</v>
+        <v>1364.076953124204</v>
       </c>
       <c r="X36" t="n">
-        <v>1634.922670856135</v>
+        <v>939.9731759066408</v>
       </c>
       <c r="Y36" t="n">
-        <v>1578.971769072161</v>
+        <v>536.5475266479192</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>738.4774805251941</v>
+        <v>839.2804483778069</v>
       </c>
       <c r="C37" t="n">
-        <v>809.0394863436298</v>
+        <v>909.8424541962427</v>
       </c>
       <c r="D37" t="n">
-        <v>866.9186304686299</v>
+        <v>967.7215983212427</v>
       </c>
       <c r="E37" t="n">
-        <v>929.3075346800429</v>
+        <v>1030.110502532656</v>
       </c>
       <c r="F37" t="n">
-        <v>998.2285072719784</v>
+        <v>1099.031475124591</v>
       </c>
       <c r="G37" t="n">
-        <v>1096.819909224437</v>
+        <v>1197.62287707705</v>
       </c>
       <c r="H37" t="n">
-        <v>1096.819909224437</v>
+        <v>1317.254822892186</v>
       </c>
       <c r="I37" t="n">
-        <v>1281.303312750684</v>
+        <v>1422.966266942499</v>
       </c>
       <c r="J37" t="n">
-        <v>1290.562963239201</v>
+        <v>1432.225917431016</v>
       </c>
       <c r="K37" t="n">
-        <v>1418.081987340004</v>
+        <v>1432.225917431016</v>
       </c>
       <c r="L37" t="n">
         <v>1432.225917431016</v>
@@ -7098,40 +7098,40 @@
         <v>1353.744740157369</v>
       </c>
       <c r="N37" t="n">
-        <v>1221.823236736723</v>
+        <v>1221.823236736724</v>
       </c>
       <c r="O37" t="n">
         <v>1012.494218541328</v>
       </c>
       <c r="P37" t="n">
-        <v>742.6826315728742</v>
+        <v>742.6826315728746</v>
       </c>
       <c r="Q37" t="n">
-        <v>410.3702412439874</v>
+        <v>410.3702412439877</v>
       </c>
       <c r="R37" t="n">
-        <v>52.56878724746122</v>
+        <v>52.5687872474615</v>
       </c>
       <c r="S37" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="T37" t="n">
-        <v>180.4254332571655</v>
+        <v>180.4254332571658</v>
       </c>
       <c r="U37" t="n">
-        <v>371.5707078626653</v>
+        <v>371.5707078626656</v>
       </c>
       <c r="V37" t="n">
-        <v>514.9521007486112</v>
+        <v>514.9521007486115</v>
       </c>
       <c r="W37" t="n">
-        <v>530.6000511556762</v>
+        <v>631.403019008289</v>
       </c>
       <c r="X37" t="n">
-        <v>626.1908421798697</v>
+        <v>726.9938100324825</v>
       </c>
       <c r="Y37" t="n">
-        <v>682.160142858902</v>
+        <v>782.9631107115148</v>
       </c>
     </row>
     <row r="38">
@@ -7141,64 +7141,64 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>450.1875243610238</v>
+        <v>450.1875243610241</v>
       </c>
       <c r="C38" t="n">
-        <v>343.6475463377976</v>
+        <v>343.6475463377979</v>
       </c>
       <c r="D38" t="n">
-        <v>276.6382981157271</v>
+        <v>276.6382981157274</v>
       </c>
       <c r="E38" t="n">
-        <v>215.6652783108093</v>
+        <v>215.6652783108096</v>
       </c>
       <c r="F38" t="n">
-        <v>154.1606028481711</v>
+        <v>154.1606028481714</v>
       </c>
       <c r="G38" t="n">
-        <v>95.22086839247731</v>
+        <v>95.22086839247763</v>
       </c>
       <c r="H38" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I38" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J38" t="n">
-        <v>128.6535720585666</v>
+        <v>128.6535720585669</v>
       </c>
       <c r="K38" t="n">
-        <v>687.0135720585666</v>
+        <v>554.2802989116057</v>
       </c>
       <c r="L38" t="n">
-        <v>1245.373572058567</v>
+        <v>774.1005953940178</v>
       </c>
       <c r="M38" t="n">
-        <v>1332.460595394003</v>
+        <v>1332.460595394018</v>
       </c>
       <c r="N38" t="n">
-        <v>1890.820595394003</v>
+        <v>1332.460595394018</v>
       </c>
       <c r="O38" t="n">
-        <v>2055.974106525702</v>
+        <v>1497.614106525717</v>
       </c>
       <c r="P38" t="n">
-        <v>2256</v>
+        <v>1697.640000000015</v>
       </c>
       <c r="Q38" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="R38" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="S38" t="n">
-        <v>2142.55934075245</v>
+        <v>2142.559340752451</v>
       </c>
       <c r="T38" t="n">
-        <v>1903.654002119973</v>
+        <v>1903.654002119974</v>
       </c>
       <c r="U38" t="n">
-        <v>1595.463361984074</v>
+        <v>1595.463361984075</v>
       </c>
       <c r="V38" t="n">
         <v>1306.724953734757</v>
@@ -7207,10 +7207,10 @@
         <v>1009.378008299457</v>
       </c>
       <c r="X38" t="n">
-        <v>758.5882775311055</v>
+        <v>758.5882775311057</v>
       </c>
       <c r="Y38" t="n">
-        <v>589.580769770695</v>
+        <v>589.5807697706953</v>
       </c>
     </row>
     <row r="39">
@@ -7220,43 +7220,43 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1460.246810961799</v>
+        <v>1107.45302683347</v>
       </c>
       <c r="C39" t="n">
-        <v>1442.974172127941</v>
+        <v>742.7056405248643</v>
       </c>
       <c r="D39" t="n">
-        <v>1091.521963140362</v>
+        <v>391.2534315372858</v>
       </c>
       <c r="E39" t="n">
-        <v>745.3885316030769</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="F39" t="n">
-        <v>745.3885316030769</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="G39" t="n">
-        <v>417.119131919897</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="H39" t="n">
-        <v>88.94000821339188</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I39" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J39" t="n">
-        <v>239.4912041375631</v>
+        <v>239.4912041375634</v>
       </c>
       <c r="K39" t="n">
-        <v>549.033930609305</v>
+        <v>549.0339306093053</v>
       </c>
       <c r="L39" t="n">
-        <v>982.2096988082787</v>
+        <v>982.2096988082791</v>
       </c>
       <c r="M39" t="n">
         <v>1257.132740551138</v>
       </c>
       <c r="N39" t="n">
-        <v>1584.25362421531</v>
+        <v>1584.253624215311</v>
       </c>
       <c r="O39" t="n">
         <v>2000.622354200916</v>
@@ -7268,28 +7268,28 @@
         <v>2177.712931092847</v>
       </c>
       <c r="R39" t="n">
-        <v>2019.599509013638</v>
+        <v>2014.280472360056</v>
       </c>
       <c r="S39" t="n">
-        <v>1909.922226792856</v>
+        <v>1904.603190139275</v>
       </c>
       <c r="T39" t="n">
-        <v>1851.009770979473</v>
+        <v>1845.690734325891</v>
       </c>
       <c r="U39" t="n">
-        <v>1794.281658395331</v>
+        <v>1788.96262174175</v>
       </c>
       <c r="V39" t="n">
-        <v>1723.058762242281</v>
+        <v>1717.739725588699</v>
       </c>
       <c r="W39" t="n">
-        <v>1633.792961323262</v>
+        <v>1628.47392466968</v>
       </c>
       <c r="X39" t="n">
-        <v>1557.163931580446</v>
+        <v>1551.844894926865</v>
       </c>
       <c r="Y39" t="n">
-        <v>1501.213029796472</v>
+        <v>1495.893993142891</v>
       </c>
     </row>
     <row r="40">
@@ -7299,34 +7299,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>839.2804483778066</v>
+        <v>648.1351737723071</v>
       </c>
       <c r="C40" t="n">
-        <v>909.8424541962423</v>
+        <v>718.6971795907428</v>
       </c>
       <c r="D40" t="n">
-        <v>967.7215983212424</v>
+        <v>776.5763237157429</v>
       </c>
       <c r="E40" t="n">
-        <v>1030.110502532655</v>
+        <v>838.9652279271559</v>
       </c>
       <c r="F40" t="n">
-        <v>1099.031475124591</v>
+        <v>907.8862005190913</v>
       </c>
       <c r="G40" t="n">
-        <v>1197.62287707705</v>
+        <v>907.8862005190913</v>
       </c>
       <c r="H40" t="n">
-        <v>1317.254822892185</v>
+        <v>1027.518146334226</v>
       </c>
       <c r="I40" t="n">
-        <v>1422.966266942499</v>
+        <v>1212.001549860473</v>
       </c>
       <c r="J40" t="n">
-        <v>1432.225917431016</v>
+        <v>1418.081987340004</v>
       </c>
       <c r="K40" t="n">
-        <v>1432.225917431016</v>
+        <v>1418.081987340004</v>
       </c>
       <c r="L40" t="n">
         <v>1432.225917431016</v>
@@ -7335,40 +7335,40 @@
         <v>1353.744740157369</v>
       </c>
       <c r="N40" t="n">
-        <v>1221.823236736723</v>
+        <v>1221.823236736724</v>
       </c>
       <c r="O40" t="n">
         <v>1012.494218541328</v>
       </c>
       <c r="P40" t="n">
-        <v>742.6826315728742</v>
+        <v>742.6826315728746</v>
       </c>
       <c r="Q40" t="n">
-        <v>410.3702412439874</v>
+        <v>410.3702412439877</v>
       </c>
       <c r="R40" t="n">
-        <v>52.5687872474612</v>
+        <v>52.5687872474615</v>
       </c>
       <c r="S40" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="T40" t="n">
-        <v>180.4254332571655</v>
+        <v>180.4254332571658</v>
       </c>
       <c r="U40" t="n">
-        <v>371.5707078626653</v>
+        <v>180.4254332571658</v>
       </c>
       <c r="V40" t="n">
-        <v>514.9521007486112</v>
+        <v>323.8068261431118</v>
       </c>
       <c r="W40" t="n">
-        <v>631.4030190082887</v>
+        <v>440.2577444027892</v>
       </c>
       <c r="X40" t="n">
-        <v>726.9938100324822</v>
+        <v>535.8485354269827</v>
       </c>
       <c r="Y40" t="n">
-        <v>782.9631107115144</v>
+        <v>591.817836106015</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>531.8064459607922</v>
+        <v>304.3039131865966</v>
       </c>
       <c r="C41" t="n">
-        <v>402.0341447052427</v>
+        <v>304.3039131865966</v>
       </c>
       <c r="D41" t="n">
-        <v>311.792573250849</v>
+        <v>214.0623417322028</v>
       </c>
       <c r="E41" t="n">
-        <v>285.362248007779</v>
+        <v>129.8569986949618</v>
       </c>
       <c r="F41" t="n">
-        <v>200.6252493128175</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="G41" t="n">
-        <v>118.4531916248005</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="H41" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I41" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J41" t="n">
-        <v>128.6535720585666</v>
+        <v>554.6552612788621</v>
       </c>
       <c r="K41" t="n">
-        <v>687.0135720585666</v>
+        <v>774.1005953940141</v>
       </c>
       <c r="L41" t="n">
-        <v>1245.373572058567</v>
+        <v>1332.460595394018</v>
       </c>
       <c r="M41" t="n">
-        <v>1803.733572058567</v>
+        <v>1332.460595394018</v>
       </c>
       <c r="N41" t="n">
-        <v>1803.733572058567</v>
+        <v>1890.820595394018</v>
       </c>
       <c r="O41" t="n">
-        <v>1968.887083190265</v>
+        <v>2055.974106525717</v>
       </c>
       <c r="P41" t="n">
-        <v>2168.912976664563</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="Q41" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="R41" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="S41" t="n">
-        <v>2112.782470977807</v>
+        <v>2112.782470977822</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.644809113007</v>
+        <v>1850.644809113022</v>
       </c>
       <c r="U41" t="n">
-        <v>1519.221845744785</v>
+        <v>1519.2218457448</v>
       </c>
       <c r="V41" t="n">
-        <v>1207.251114263144</v>
+        <v>1207.251114263159</v>
       </c>
       <c r="W41" t="n">
-        <v>886.6718455955204</v>
+        <v>886.6718455955354</v>
       </c>
       <c r="X41" t="n">
-        <v>886.6718455955204</v>
+        <v>612.649791594861</v>
       </c>
       <c r="Y41" t="n">
-        <v>694.4320146027867</v>
+        <v>420.4099606021272</v>
       </c>
     </row>
     <row r="42">
@@ -7457,43 +7457,43 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>161.5139162210097</v>
+        <v>1004.672216904155</v>
       </c>
       <c r="C42" t="n">
-        <v>121.0089541548285</v>
+        <v>639.9248305955493</v>
       </c>
       <c r="D42" t="n">
-        <v>93.79916940967435</v>
+        <v>288.4726216079709</v>
       </c>
       <c r="E42" t="n">
-        <v>71.90816211481311</v>
+        <v>266.5816143131096</v>
       </c>
       <c r="F42" t="n">
-        <v>53.08367490483649</v>
+        <v>247.757127103133</v>
       </c>
       <c r="G42" t="n">
-        <v>49.05669946408082</v>
+        <v>49.05669946408111</v>
       </c>
       <c r="H42" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I42" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J42" t="n">
-        <v>239.4912041375631</v>
+        <v>239.4912041375634</v>
       </c>
       <c r="K42" t="n">
-        <v>549.033930609305</v>
+        <v>549.0339306093053</v>
       </c>
       <c r="L42" t="n">
-        <v>982.2096988082787</v>
+        <v>982.2096988082791</v>
       </c>
       <c r="M42" t="n">
         <v>1257.132740551138</v>
       </c>
       <c r="N42" t="n">
-        <v>1584.25362421531</v>
+        <v>1584.253624215311</v>
       </c>
       <c r="O42" t="n">
         <v>2000.622354200916</v>
@@ -7505,7 +7505,7 @@
         <v>2255.471670368536</v>
       </c>
       <c r="R42" t="n">
-        <v>2074.125925057003</v>
+        <v>2074.125925057004</v>
       </c>
       <c r="S42" t="n">
         <v>1941.216319603899</v>
@@ -7514,19 +7514,19 @@
         <v>1859.071540558192</v>
       </c>
       <c r="U42" t="n">
-        <v>1584.437652543431</v>
+        <v>1779.111104741728</v>
       </c>
       <c r="V42" t="n">
-        <v>1165.740008915633</v>
+        <v>1684.655885356354</v>
       </c>
       <c r="W42" t="n">
-        <v>728.9994605218668</v>
+        <v>1247.915336962587</v>
       </c>
       <c r="X42" t="n">
-        <v>629.1381075467278</v>
+        <v>1148.053983987448</v>
       </c>
       <c r="Y42" t="n">
-        <v>225.7124582880062</v>
+        <v>1068.870758971151</v>
       </c>
     </row>
     <row r="43">
@@ -7536,25 +7536,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>668.7869414962938</v>
+        <v>679.890448377807</v>
       </c>
       <c r="C43" t="n">
-        <v>716.5789473147296</v>
+        <v>727.6824541962428</v>
       </c>
       <c r="D43" t="n">
-        <v>751.6880914397296</v>
+        <v>762.7915983212429</v>
       </c>
       <c r="E43" t="n">
-        <v>791.3069956511426</v>
+        <v>802.4105025326559</v>
       </c>
       <c r="F43" t="n">
-        <v>837.4579682430781</v>
+        <v>848.5614751245913</v>
       </c>
       <c r="G43" t="n">
-        <v>913.2793701955371</v>
+        <v>924.3828770770504</v>
       </c>
       <c r="H43" t="n">
-        <v>1010.141316010672</v>
+        <v>1021.244822892186</v>
       </c>
       <c r="I43" t="n">
         <v>1171.854719536919</v>
@@ -7572,40 +7572,40 @@
         <v>1493.138679551308</v>
       </c>
       <c r="N43" t="n">
-        <v>1337.984852898339</v>
+        <v>1337.98485289834</v>
       </c>
       <c r="O43" t="n">
         <v>1105.423511470621</v>
       </c>
       <c r="P43" t="n">
-        <v>812.3796012698439</v>
+        <v>812.3796012698442</v>
       </c>
       <c r="Q43" t="n">
-        <v>456.8348877086338</v>
+        <v>456.8348877086341</v>
       </c>
       <c r="R43" t="n">
-        <v>75.80111047978446</v>
+        <v>75.80111047978474</v>
       </c>
       <c r="S43" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="T43" t="n">
-        <v>157.6554332571655</v>
+        <v>157.6554332571658</v>
       </c>
       <c r="U43" t="n">
-        <v>326.0307078626653</v>
+        <v>326.0307078626656</v>
       </c>
       <c r="V43" t="n">
-        <v>446.6421007486113</v>
+        <v>446.6421007486116</v>
       </c>
       <c r="W43" t="n">
-        <v>540.3230190082886</v>
+        <v>540.3230190082891</v>
       </c>
       <c r="X43" t="n">
-        <v>613.1438100324822</v>
+        <v>613.1438100324826</v>
       </c>
       <c r="Y43" t="n">
-        <v>635.2396038300017</v>
+        <v>646.3431107115149</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>531.8064459607922</v>
+        <v>257.7843919601328</v>
       </c>
       <c r="C44" t="n">
-        <v>402.0341447052427</v>
+        <v>257.7843919601328</v>
       </c>
       <c r="D44" t="n">
-        <v>311.792573250849</v>
+        <v>167.542820505739</v>
       </c>
       <c r="E44" t="n">
-        <v>285.362248007779</v>
+        <v>83.33747746849797</v>
       </c>
       <c r="F44" t="n">
-        <v>200.6252493128175</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="G44" t="n">
-        <v>118.4531916248006</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="H44" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I44" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J44" t="n">
-        <v>128.6535720585666</v>
+        <v>554.6552612788621</v>
       </c>
       <c r="K44" t="n">
-        <v>687.0135720585666</v>
+        <v>774.1005953940139</v>
       </c>
       <c r="L44" t="n">
-        <v>1245.373572058567</v>
+        <v>1332.460595394018</v>
       </c>
       <c r="M44" t="n">
-        <v>1332.460595394003</v>
+        <v>1890.820595394018</v>
       </c>
       <c r="N44" t="n">
-        <v>1890.820595394003</v>
+        <v>1890.820595394018</v>
       </c>
       <c r="O44" t="n">
-        <v>2055.974106525702</v>
+        <v>2055.974106525717</v>
       </c>
       <c r="P44" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="Q44" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="R44" t="n">
-        <v>2256</v>
+        <v>2256.000000000015</v>
       </c>
       <c r="S44" t="n">
-        <v>2112.782470977807</v>
+        <v>2112.782470977822</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.644809113007</v>
+        <v>1850.644809113022</v>
       </c>
       <c r="U44" t="n">
-        <v>1519.221845744785</v>
+        <v>1519.2218457448</v>
       </c>
       <c r="V44" t="n">
-        <v>1207.251114263144</v>
+        <v>1207.251114263159</v>
       </c>
       <c r="W44" t="n">
-        <v>886.6718455955204</v>
+        <v>886.6718455955354</v>
       </c>
       <c r="X44" t="n">
-        <v>886.6718455955204</v>
+        <v>612.649791594861</v>
       </c>
       <c r="Y44" t="n">
-        <v>694.4320146027867</v>
+        <v>420.4099606021272</v>
       </c>
     </row>
     <row r="45">
@@ -7694,43 +7694,43 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>680.4297926617301</v>
+        <v>809.9987647058585</v>
       </c>
       <c r="C45" t="n">
-        <v>639.924830595549</v>
+        <v>445.2513783972531</v>
       </c>
       <c r="D45" t="n">
-        <v>612.7150458503949</v>
+        <v>93.79916940967466</v>
       </c>
       <c r="E45" t="n">
-        <v>590.8240385555337</v>
+        <v>71.90816211481342</v>
       </c>
       <c r="F45" t="n">
-        <v>377.3260991472607</v>
+        <v>53.08367490483678</v>
       </c>
       <c r="G45" t="n">
-        <v>49.05669946408081</v>
+        <v>49.05669946408113</v>
       </c>
       <c r="H45" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="I45" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="J45" t="n">
-        <v>239.4912041375631</v>
+        <v>239.4912041375634</v>
       </c>
       <c r="K45" t="n">
-        <v>549.033930609305</v>
+        <v>549.0339306093053</v>
       </c>
       <c r="L45" t="n">
-        <v>982.2096988082787</v>
+        <v>982.2096988082791</v>
       </c>
       <c r="M45" t="n">
         <v>1257.132740551138</v>
       </c>
       <c r="N45" t="n">
-        <v>1584.25362421531</v>
+        <v>1584.253624215311</v>
       </c>
       <c r="O45" t="n">
         <v>2000.622354200916</v>
@@ -7742,28 +7742,28 @@
         <v>2255.471670368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1749.883500814579</v>
+        <v>2074.125925057004</v>
       </c>
       <c r="S45" t="n">
-        <v>1616.973895361475</v>
+        <v>1941.216319603899</v>
       </c>
       <c r="T45" t="n">
-        <v>1534.829116315768</v>
+        <v>1859.071540558192</v>
       </c>
       <c r="U45" t="n">
-        <v>1454.868680499303</v>
+        <v>1779.111104741728</v>
       </c>
       <c r="V45" t="n">
-        <v>1360.413461113929</v>
+        <v>1684.655885356354</v>
       </c>
       <c r="W45" t="n">
-        <v>1247.915336962587</v>
+        <v>1572.157761205012</v>
       </c>
       <c r="X45" t="n">
-        <v>1148.053983987448</v>
+        <v>1472.296408229873</v>
       </c>
       <c r="Y45" t="n">
-        <v>744.6283347287266</v>
+        <v>1068.870758971151</v>
       </c>
     </row>
     <row r="46">
@@ -7803,7 +7803,7 @@
         <v>1603.653394126239</v>
       </c>
       <c r="L46" t="n">
-        <v>1594.852180057278</v>
+        <v>1594.852180057279</v>
       </c>
       <c r="M46" t="n">
         <v>1493.138679551308</v>
@@ -7815,28 +7815,28 @@
         <v>1105.423511470621</v>
       </c>
       <c r="P46" t="n">
-        <v>812.379601269844</v>
+        <v>812.3796012698442</v>
       </c>
       <c r="Q46" t="n">
-        <v>456.8348877086339</v>
+        <v>456.8348877086341</v>
       </c>
       <c r="R46" t="n">
-        <v>75.80111047978443</v>
+        <v>75.80111047978475</v>
       </c>
       <c r="S46" t="n">
-        <v>45.12</v>
+        <v>45.1200000000003</v>
       </c>
       <c r="T46" t="n">
-        <v>157.6554332571655</v>
+        <v>157.6554332571658</v>
       </c>
       <c r="U46" t="n">
-        <v>326.0307078626653</v>
+        <v>314.9272009811527</v>
       </c>
       <c r="V46" t="n">
-        <v>446.6421007486113</v>
+        <v>435.5385938670987</v>
       </c>
       <c r="W46" t="n">
-        <v>540.3230190082886</v>
+        <v>529.2195121267761</v>
       </c>
       <c r="X46" t="n">
         <v>602.0403031509696</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>248.0502805878619</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M2" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
         <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>301.3692255388389</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8438,22 +8438,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
         <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
-        <v>235.5012052109776</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M8" t="n">
-        <v>472.2608914614128</v>
+        <v>772.4711016975159</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>417.5114925321142</v>
+        <v>470.019849246231</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>166.1869066997265</v>
       </c>
       <c r="M11" t="n">
         <v>946.1990623156843</v>
       </c>
       <c r="N11" t="n">
-        <v>875.1881540497347</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8915,19 +8915,19 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>470.0198492462312</v>
       </c>
       <c r="L14" t="n">
-        <v>417.5114925321142</v>
+        <v>114.3133717017404</v>
       </c>
       <c r="M14" t="n">
-        <v>946.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N14" t="n">
         <v>875.1881540497347</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>482.1782715841426</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -9389,13 +9389,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>263.2741006722111</v>
+        <v>470.019849246231</v>
       </c>
       <c r="L20" t="n">
         <v>426.9592964824121</v>
       </c>
       <c r="M20" t="n">
-        <v>297.1990623156842</v>
+        <v>685.4266725329983</v>
       </c>
       <c r="N20" t="n">
         <v>226.1881540497347</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>263.2741006722111</v>
       </c>
       <c r="L23" t="n">
-        <v>41.23339715462316</v>
+        <v>426.9592964824121</v>
       </c>
       <c r="M23" t="n">
         <v>297.1990623156842</v>
       </c>
       <c r="N23" t="n">
-        <v>875.1881540497347</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>471.0198492462312</v>
       </c>
       <c r="L26" t="n">
-        <v>427.9592964824121</v>
+        <v>427.9592964824119</v>
       </c>
       <c r="M26" t="n">
-        <v>687.3862684925944</v>
+        <v>669.7373621234972</v>
       </c>
       <c r="N26" t="n">
         <v>226.1881540497347</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>447.9536429552543</v>
       </c>
       <c r="Q26" t="n">
         <v>20.87871447823917</v>
@@ -10097,16 +10097,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>471.0198492462312</v>
+        <v>419.4710884917101</v>
       </c>
       <c r="L29" t="n">
-        <v>168.1465026593223</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>297.1990623156842</v>
+        <v>947.1990623156843</v>
       </c>
       <c r="N29" t="n">
         <v>876.1881540497347</v>
@@ -10337,13 +10337,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>471.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>427.9592964824119</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>467.6910050787511</v>
+        <v>771.69679201606</v>
       </c>
       <c r="N32" t="n">
         <v>876.1881540497347</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,10 +10574,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>250.9458359664578</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>250.9458359664723</v>
       </c>
       <c r="M35" t="n">
         <v>861.1990623156843</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>385.0198492462312</v>
+        <v>250.9458359664723</v>
       </c>
       <c r="L38" t="n">
-        <v>341.9592964824121</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>385.1657525534988</v>
+        <v>861.1990623156843</v>
       </c>
       <c r="N38" t="n">
-        <v>790.1881540497347</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20.87871447823917</v>
+        <v>584.8787144782393</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>385.0198492462312</v>
+        <v>42.68180289789984</v>
       </c>
       <c r="L41" t="n">
-        <v>341.9592964824121</v>
+        <v>341.9592964824158</v>
       </c>
       <c r="M41" t="n">
-        <v>861.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N41" t="n">
-        <v>226.1881540497347</v>
+        <v>790.1881540497347</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>108.845404716054</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>385.0198492462312</v>
+        <v>42.68180289789962</v>
       </c>
       <c r="L44" t="n">
-        <v>341.9592964824121</v>
+        <v>341.9592964824158</v>
       </c>
       <c r="M44" t="n">
-        <v>385.1657525534988</v>
+        <v>861.1990623156845</v>
       </c>
       <c r="N44" t="n">
-        <v>790.1881540497347</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.139355938714289e-13</v>
+        <v>1.717292974490192e-12</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.479101076896995</v>
+        <v>6.479101076881904</v>
       </c>
     </row>
     <row r="36">
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>6.479101076896853</v>
+        <v>6.479101076882444</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>46.05432601419915</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>57.19726761622935</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>271.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25833,22 +25833,22 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>57.1972676162294</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>46.05432601419917</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>271.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9911642.155143701</v>
+        <v>9911642.155143702</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10729902.00267017</v>
+        <v>10729902.00267018</v>
       </c>
     </row>
     <row r="15">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12333101.13772312</v>
+        <v>12333101.13772313</v>
       </c>
     </row>
   </sheetData>
@@ -26272,10 +26272,10 @@
         <v>1385314.744365854</v>
       </c>
       <c r="C2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365855</v>
       </c>
       <c r="D2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365855</v>
       </c>
       <c r="E2" t="n">
         <v>1385314.744365855</v>
@@ -26284,7 +26284,7 @@
         <v>1385314.744365855</v>
       </c>
       <c r="G2" t="n">
-        <v>1385314.744365855</v>
+        <v>1385314.744365854</v>
       </c>
       <c r="H2" t="n">
         <v>1385314.744365855</v>
@@ -26293,7 +26293,7 @@
         <v>1385314.744365855</v>
       </c>
       <c r="J2" t="n">
-        <v>1385314.744365855</v>
+        <v>1385314.744365854</v>
       </c>
       <c r="K2" t="n">
         <v>1385314.744365855</v>
@@ -26302,16 +26302,16 @@
         <v>1385314.744365855</v>
       </c>
       <c r="M2" t="n">
-        <v>1384747.434275561</v>
+        <v>1384747.434275562</v>
       </c>
       <c r="N2" t="n">
-        <v>1384747.434275561</v>
+        <v>1384747.434275562</v>
       </c>
       <c r="O2" t="n">
-        <v>1356553.114275562</v>
+        <v>1356553.114275563</v>
       </c>
       <c r="P2" t="n">
-        <v>1356553.114275562</v>
+        <v>1356553.114275563</v>
       </c>
     </row>
     <row r="3">
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>84928</v>
+        <v>84928.00000000132</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>602219.8615549036</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.25402263</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.2919515911</v>
       </c>
       <c r="E4" t="n">
-        <v>513253.1653847605</v>
+        <v>513056.3660364837</v>
       </c>
       <c r="F4" t="n">
-        <v>511570.4197316588</v>
+        <v>511373.620383382</v>
       </c>
       <c r="G4" t="n">
-        <v>509885.3519526902</v>
+        <v>509688.5526044134</v>
       </c>
       <c r="H4" t="n">
-        <v>508197.9453958013</v>
+        <v>508001.1460475244</v>
       </c>
       <c r="I4" t="n">
-        <v>506508.1831919707</v>
+        <v>506311.3838436939</v>
       </c>
       <c r="J4" t="n">
-        <v>504742.7776510159</v>
+        <v>504545.7862134472</v>
       </c>
       <c r="K4" t="n">
-        <v>503048.9703867822</v>
+        <v>502851.9789492135</v>
       </c>
       <c r="L4" t="n">
-        <v>501352.7565448462</v>
+        <v>501155.7651072776</v>
       </c>
       <c r="M4" t="n">
-        <v>505436.0855019934</v>
+        <v>505255.613743524</v>
       </c>
       <c r="N4" t="n">
-        <v>503674.4115882328</v>
+        <v>503493.9398297633</v>
       </c>
       <c r="O4" t="n">
-        <v>488048.4258486072</v>
+        <v>487867.9540901377</v>
       </c>
       <c r="P4" t="n">
-        <v>486341.4239479515</v>
+        <v>486160.9521894821</v>
       </c>
     </row>
     <row r="5">
@@ -26458,16 +26458,16 @@
         <v>74136.149</v>
       </c>
       <c r="M5" t="n">
-        <v>70840.936</v>
+        <v>70840.93600000023</v>
       </c>
       <c r="N5" t="n">
-        <v>70840.936</v>
+        <v>70840.93600000023</v>
       </c>
       <c r="O5" t="n">
-        <v>68907.349</v>
+        <v>68907.34900000023</v>
       </c>
       <c r="P5" t="n">
-        <v>68907.349</v>
+        <v>68907.34900000023</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>493207.1681557354</v>
+        <v>493406.4828109506</v>
       </c>
       <c r="C6" t="n">
-        <v>726314.0903432241</v>
+        <v>726513.4049984395</v>
       </c>
       <c r="D6" t="n">
-        <v>728325.737759048</v>
+        <v>728525.0524142637</v>
       </c>
       <c r="E6" t="n">
-        <v>202586.2299810944</v>
+        <v>202783.0293293709</v>
       </c>
       <c r="F6" t="n">
-        <v>799668.9756341958</v>
+        <v>799865.7749824726</v>
       </c>
       <c r="G6" t="n">
-        <v>801354.0434131647</v>
+        <v>801550.842761441</v>
       </c>
       <c r="H6" t="n">
-        <v>803041.4499700534</v>
+        <v>803238.2493183304</v>
       </c>
       <c r="I6" t="n">
-        <v>804731.2121738839</v>
+        <v>804928.0115221612</v>
       </c>
       <c r="J6" t="n">
-        <v>417635.817714839</v>
+        <v>417832.8091524072</v>
       </c>
       <c r="K6" t="n">
-        <v>808129.6249790727</v>
+        <v>808326.6164166412</v>
       </c>
       <c r="L6" t="n">
-        <v>809825.8388210087</v>
+        <v>810022.8302585774</v>
       </c>
       <c r="M6" t="n">
-        <v>723542.4127735678</v>
+        <v>723722.8845320366</v>
       </c>
       <c r="N6" t="n">
-        <v>810232.0866873285</v>
+        <v>810412.5584457989</v>
       </c>
       <c r="O6" t="n">
-        <v>561197.3394269544</v>
+        <v>561377.8111854246</v>
       </c>
       <c r="P6" t="n">
-        <v>801304.3413276103</v>
+        <v>801484.8130860809</v>
       </c>
     </row>
   </sheetData>
@@ -26892,16 +26892,16 @@
         <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>564</v>
+        <v>564.0000000000038</v>
       </c>
       <c r="N4" t="n">
-        <v>564</v>
+        <v>564.0000000000038</v>
       </c>
       <c r="O4" t="n">
-        <v>564</v>
+        <v>564.0000000000038</v>
       </c>
       <c r="P4" t="n">
-        <v>564</v>
+        <v>564.0000000000038</v>
       </c>
     </row>
   </sheetData>
@@ -26993,13 +26993,13 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27030,7 +27030,7 @@
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>248</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>223.322091864989</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321723</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27557,25 +27557,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
+        <v>63.9130158896312</v>
+      </c>
+      <c r="U3" t="n">
         <v>400</v>
-      </c>
-      <c r="U3" t="n">
-        <v>26.1959257979226</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>230.1547495649198</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27594,10 +27594,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>347.6775194675577</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27612,7 +27612,7 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>175.7723657795152</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>396.2647849014816</v>
@@ -27621,7 +27621,7 @@
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
         <v>209.2386648669134</v>
@@ -27682,10 +27682,10 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
+        <v>400</v>
+      </c>
+      <c r="G5" t="n">
         <v>398.2013121321735</v>
-      </c>
-      <c r="G5" t="n">
-        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
+        <v>245.1326461704237</v>
+      </c>
+      <c r="T6" t="n">
         <v>400</v>
-      </c>
-      <c r="T6" t="n">
-        <v>246.6867672954181</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27846,19 +27846,19 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>381.2726298395087</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014815</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27888,13 +27888,13 @@
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>252.2231630720599</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>338.5868575707302</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -27998,10 +27998,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>330.0491815260438</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28046,16 +28046,16 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>295.3942944519113</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>282.6683395005035</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>244.8599384153005</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>377.0173452653286</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,10 +28116,10 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>94.44753714149141</v>
+        <v>94.44753714149138</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
@@ -28235,7 +28235,7 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28268,16 +28268,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>128.2732823236868</v>
       </c>
       <c r="S12" t="n">
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
@@ -28286,13 +28286,13 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>205.2544342066192</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28311,7 +28311,7 @@
         <v>321</v>
       </c>
       <c r="E13" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="F13" t="n">
         <v>321</v>
@@ -28362,7 +28362,7 @@
         <v>321</v>
       </c>
       <c r="V13" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
       <c r="W13" t="n">
         <v>321</v>
@@ -28472,13 +28472,13 @@
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>205.254434206619</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I15" t="n">
         <v>191.2065745705938</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28517,7 +28517,7 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>128.2732823236867</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -28529,7 +28529,7 @@
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28605,10 +28605,10 @@
         <v>321</v>
       </c>
       <c r="X16" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="Y16" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
     </row>
     <row r="17">
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>319.6111010768972</v>
+        <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>95.83643606459415</v>
+        <v>94.44753714149138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28709,7 +28709,7 @@
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28763,10 +28763,10 @@
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>128.2732823236867</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>128.2732823236871</v>
       </c>
     </row>
     <row r="19">
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>94.44753714149138</v>
+        <v>94.44753714149141</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28937,16 +28937,16 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29013,7 +29013,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="C22" t="n">
         <v>321</v>
@@ -29040,7 +29040,7 @@
         <v>321</v>
       </c>
       <c r="K22" t="n">
-        <v>309.7843364833207</v>
+        <v>321</v>
       </c>
       <c r="L22" t="n">
         <v>321</v>
@@ -29140,10 +29140,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>162.4939254614603</v>
+        <v>161.1050265383575</v>
       </c>
       <c r="S23" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="T23" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29234,13 +29234,13 @@
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>128.273282323687</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29274,7 +29274,7 @@
         <v>321</v>
       </c>
       <c r="J25" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="K25" t="n">
         <v>321</v>
@@ -29304,7 +29304,7 @@
         <v>321</v>
       </c>
       <c r="T25" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="U25" t="n">
         <v>321</v>
@@ -29332,7 +29332,7 @@
         <v>321</v>
       </c>
       <c r="C26" t="n">
-        <v>315.7303010768971</v>
+        <v>321</v>
       </c>
       <c r="D26" t="n">
         <v>321</v>
@@ -29398,7 +29398,7 @@
         <v>321</v>
       </c>
       <c r="Y26" t="n">
-        <v>321</v>
+        <v>315.7303010768973</v>
       </c>
     </row>
     <row r="27">
@@ -29408,22 +29408,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>205.2544342066192</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
         <v>321</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29499,10 +29499,10 @@
         <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>309.7843364833201</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
-        <v>321</v>
+        <v>309.7843364833202</v>
       </c>
       <c r="H28" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>315.7303010768973</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
         <v>95.83643606459415</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>162.4939254614603</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29648,7 +29648,7 @@
         <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>128.2732823236869</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -29657,7 +29657,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29714,7 +29714,7 @@
         <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>321</v>
+        <v>128.2732823236871</v>
       </c>
     </row>
     <row r="31">
@@ -29733,13 +29733,13 @@
         <v>321</v>
       </c>
       <c r="E31" t="n">
+        <v>321</v>
+      </c>
+      <c r="F31" t="n">
+        <v>321</v>
+      </c>
+      <c r="G31" t="n">
         <v>309.7843364833202</v>
-      </c>
-      <c r="F31" t="n">
-        <v>321</v>
-      </c>
-      <c r="G31" t="n">
-        <v>321</v>
       </c>
       <c r="H31" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>315.7303010768973</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>95.83643606459415</v>
@@ -29854,7 +29854,7 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S32" t="n">
-        <v>321</v>
+        <v>315.7303010768973</v>
       </c>
       <c r="T32" t="n">
         <v>321</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>128.2732823236867</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29945,7 +29945,7 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>321</v>
@@ -30125,13 +30125,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>263.0809046081088</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>324.9867056863481</v>
@@ -30140,7 +30140,7 @@
         <v>324.89733246944</v>
       </c>
       <c r="I36" t="n">
-        <v>104.5958187384925</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30179,16 +30179,16 @@
         <v>344</v>
       </c>
       <c r="V36" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>344</v>
       </c>
       <c r="X36" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30216,19 +30216,19 @@
         <v>344</v>
       </c>
       <c r="H37" t="n">
-        <v>223.1596506917826</v>
+        <v>344</v>
       </c>
       <c r="I37" t="n">
-        <v>344</v>
+        <v>264.4323641657242</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>344</v>
+        <v>215.192904948684</v>
       </c>
       <c r="L37" t="n">
-        <v>344</v>
+        <v>329.713201928271</v>
       </c>
       <c r="M37" t="n">
         <v>344</v>
@@ -30261,7 +30261,7 @@
         <v>344</v>
       </c>
       <c r="W37" t="n">
-        <v>242.1788203508965</v>
+        <v>344</v>
       </c>
       <c r="X37" t="n">
         <v>344</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -30371,13 +30371,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I39" t="n">
-        <v>147.8247664393359</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,7 +30404,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>344</v>
+        <v>338.7341537129537</v>
       </c>
       <c r="S39" t="n">
         <v>344</v>
@@ -30450,22 +30450,22 @@
         <v>344</v>
       </c>
       <c r="G40" t="n">
-        <v>344</v>
+        <v>244.4127253005464</v>
       </c>
       <c r="H40" t="n">
         <v>344</v>
       </c>
       <c r="I40" t="n">
-        <v>264.4323641657242</v>
+        <v>344</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>198.8088757484993</v>
       </c>
       <c r="K40" t="n">
         <v>215.192904948684</v>
       </c>
       <c r="L40" t="n">
-        <v>329.713201928271</v>
+        <v>344</v>
       </c>
       <c r="M40" t="n">
         <v>344</v>
@@ -30492,7 +30492,7 @@
         <v>344</v>
       </c>
       <c r="U40" t="n">
-        <v>344</v>
+        <v>150.9239650449497</v>
       </c>
       <c r="V40" t="n">
         <v>344</v>
@@ -30596,10 +30596,10 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
@@ -30608,7 +30608,7 @@
         <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>128.2732823236867</v>
       </c>
       <c r="H42" t="n">
         <v>321</v>
@@ -30650,10 +30650,10 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>128.2732823236871</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -30662,7 +30662,7 @@
         <v>321</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43">
@@ -30693,7 +30693,7 @@
         <v>321</v>
       </c>
       <c r="I43" t="n">
-        <v>321</v>
+        <v>309.7843364833202</v>
       </c>
       <c r="J43" t="n">
         <v>321</v>
@@ -30741,7 +30741,7 @@
         <v>321</v>
       </c>
       <c r="Y43" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44">
@@ -30830,22 +30830,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>128.2732823236867</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H45" t="n">
         <v>321</v>
@@ -30878,7 +30878,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
         <v>321</v>
@@ -30966,7 +30966,7 @@
         <v>321</v>
       </c>
       <c r="U46" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="V46" t="n">
         <v>321</v>
@@ -30975,7 +30975,7 @@
         <v>321</v>
       </c>
       <c r="X46" t="n">
-        <v>309.7843364833207</v>
+        <v>321</v>
       </c>
       <c r="Y46" t="n">
         <v>321</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>374</v>
       </c>
-      <c r="K2" t="n">
-        <v>300.2102102361031</v>
-      </c>
       <c r="L2" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="M2" t="n">
         <v>374</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>300.2102102361032</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,10 +34880,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>62.14130141200219</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34898,7 +34898,7 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>4.670319995462439</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
         <v>374</v>
@@ -34907,7 +34907,7 @@
         <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698063</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -35132,10 +35132,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>154.1368480001852</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
@@ -35144,7 +35144,7 @@
         <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35174,13 +35174,13 @@
         <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.779517641952335</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35217,22 +35217,22 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>374</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>373.9999999999999</v>
       </c>
-      <c r="L8" t="n">
-        <v>300.2102102361032</v>
-      </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>300.2102102361031</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>374</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>58.67867865278593</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>8.285483532761582</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>149.8815634260051</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U10" t="n">
         <v>249.0516415124273</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K11" t="n">
-        <v>596.491643285883</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>222.040703517588</v>
+        <v>388.2276102173143</v>
       </c>
       <c r="M11" t="n">
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>166.8217284158573</v>
@@ -35597,16 +35597,16 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E13" t="n">
-        <v>40.01909516304346</v>
+        <v>28.80343164636386</v>
       </c>
       <c r="F13" t="n">
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H13" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I13" t="n">
         <v>163.3468722487342</v>
@@ -35648,7 +35648,7 @@
         <v>170.0760349550503</v>
       </c>
       <c r="V13" t="n">
-        <v>110.6140262671042</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W13" t="n">
         <v>94.62719016129032</v>
@@ -35694,19 +35694,19 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K14" t="n">
-        <v>178.9801507537688</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
-        <v>639.5521960497022</v>
+        <v>336.3540752193284</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>649</v>
       </c>
       <c r="O14" t="n">
-        <v>166.8217284158573</v>
+        <v>649</v>
       </c>
       <c r="P14" t="n">
         <v>202.0463570447457</v>
@@ -35891,10 +35891,10 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X16" t="n">
-        <v>62.34069105321293</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y16" t="n">
-        <v>33.53464715053764</v>
+        <v>22.31898363385807</v>
       </c>
     </row>
     <row r="17">
@@ -36168,13 +36168,13 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K20" t="n">
-        <v>442.25425142598</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>649</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>388.2276102173141</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -36186,7 +36186,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q20" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33.88619966292134</v>
+        <v>22.6705361462418</v>
       </c>
       <c r="C22" t="n">
         <v>48.27475335195533</v>
@@ -36314,10 +36314,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G22" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H22" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I22" t="n">
         <v>163.3468722487342</v>
@@ -36326,7 +36326,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K22" t="n">
-        <v>94.59143153463661</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36405,16 +36405,16 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K23" t="n">
-        <v>178.9801507537688</v>
+        <v>442.25425142598</v>
       </c>
       <c r="L23" t="n">
-        <v>263.2741006722111</v>
+        <v>649</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>166.8217284158573</v>
@@ -36560,7 +36560,7 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J25" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949537</v>
       </c>
       <c r="K25" t="n">
         <v>105.807095051316</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>102.456491288538</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U25" t="n">
         <v>170.0760349550503</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K26" t="n">
         <v>650</v>
       </c>
       <c r="L26" t="n">
-        <v>650</v>
+        <v>649.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>390.1872061769101</v>
+        <v>372.538299807813</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>166.8217284158573</v>
       </c>
       <c r="P26" t="n">
-        <v>202.0463570447457</v>
+        <v>650</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36785,13 +36785,13 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>35.40148051557823</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>76.58727469945359</v>
+        <v>65.37161118277378</v>
       </c>
       <c r="H28" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I28" t="n">
         <v>163.3468722487342</v>
@@ -36876,16 +36876,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K29" t="n">
+        <v>598.451239245479</v>
+      </c>
+      <c r="L29" t="n">
+        <v>222.040703517588</v>
+      </c>
+      <c r="M29" t="n">
         <v>650</v>
-      </c>
-      <c r="L29" t="n">
-        <v>390.1872061769102</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>650</v>
@@ -37019,16 +37019,16 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E31" t="n">
-        <v>28.80343164636363</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F31" t="n">
         <v>46.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>76.58727469945357</v>
+        <v>65.37161118277378</v>
       </c>
       <c r="H31" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I31" t="n">
         <v>163.3468722487342</v>
@@ -37116,13 +37116,13 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K32" t="n">
-        <v>650</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L32" t="n">
-        <v>649.9999999999999</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M32" t="n">
-        <v>170.491942763067</v>
+        <v>474.4977297003759</v>
       </c>
       <c r="N32" t="n">
         <v>650</v>
@@ -37134,7 +37134,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37262,10 +37262,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G34" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H34" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I34" t="n">
         <v>163.3468722487342</v>
@@ -37353,16 +37353,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K35" t="n">
-        <v>429.9259867202267</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L35" t="n">
-        <v>222.040703517588</v>
+        <v>472.9865394840603</v>
       </c>
       <c r="M35" t="n">
-        <v>564</v>
+        <v>564.0000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>564</v>
+        <v>564.0000000000001</v>
       </c>
       <c r="O35" t="n">
         <v>166.8217284158573</v>
@@ -37499,22 +37499,22 @@
         <v>69.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>99.58727469945359</v>
+        <v>99.58727469945357</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>120.8403493082175</v>
       </c>
       <c r="I37" t="n">
-        <v>186.3468722487342</v>
+        <v>106.7792364144583</v>
       </c>
       <c r="J37" t="n">
         <v>9.353182311633219</v>
       </c>
       <c r="K37" t="n">
-        <v>128.807095051316</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>14.28679807172904</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>144.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>15.80601051218684</v>
+        <v>117.6271901612903</v>
       </c>
       <c r="X37" t="n">
         <v>96.55635456989245</v>
@@ -37590,16 +37590,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K38" t="n">
-        <v>564</v>
+        <v>429.9259867202412</v>
       </c>
       <c r="L38" t="n">
+        <v>222.040703517588</v>
+      </c>
+      <c r="M38" t="n">
         <v>564.0000000000001</v>
       </c>
-      <c r="M38" t="n">
-        <v>87.96669023781462</v>
-      </c>
       <c r="N38" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>166.8217284158573</v>
@@ -37608,7 +37608,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>564.0000000000001</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37736,22 +37736,22 @@
         <v>69.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>99.58727469945357</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>120.8403493082175</v>
       </c>
       <c r="I40" t="n">
-        <v>106.7792364144583</v>
+        <v>186.3468722487342</v>
       </c>
       <c r="J40" t="n">
-        <v>9.353182311633219</v>
+        <v>208.1620580601325</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>14.28679807172902</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37778,7 +37778,7 @@
         <v>136.6721548052177</v>
       </c>
       <c r="U40" t="n">
-        <v>193.0760349550503</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>144.8296897837838</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K41" t="n">
-        <v>564</v>
+        <v>221.6619536516687</v>
       </c>
       <c r="L41" t="n">
+        <v>564.0000000000038</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>564.0000000000001</v>
-      </c>
-      <c r="M41" t="n">
-        <v>564</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>166.8217284158573</v>
@@ -37845,7 +37845,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q41" t="n">
-        <v>87.96669023781484</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37973,13 +37973,13 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H43" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I43" t="n">
-        <v>163.3468722487342</v>
+        <v>152.1312087320543</v>
       </c>
       <c r="J43" t="n">
         <v>330.3531823116332</v>
@@ -38027,7 +38027,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>22.31898363385807</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="44">
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K44" t="n">
-        <v>564</v>
+        <v>221.6619536516685</v>
       </c>
       <c r="L44" t="n">
-        <v>564.0000000000001</v>
+        <v>564.0000000000038</v>
       </c>
       <c r="M44" t="n">
-        <v>87.96669023781462</v>
+        <v>564.0000000000003</v>
       </c>
       <c r="N44" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>166.8217284158573</v>
@@ -38210,10 +38210,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H46" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I46" t="n">
         <v>163.3468722487342</v>
@@ -38252,7 +38252,7 @@
         <v>113.6721548052177</v>
       </c>
       <c r="U46" t="n">
-        <v>170.0760349550503</v>
+        <v>158.8603714383705</v>
       </c>
       <c r="V46" t="n">
         <v>121.8296897837838</v>
@@ -38261,7 +38261,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X46" t="n">
-        <v>62.34069105321316</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y46" t="n">
         <v>33.53464715053764</v>
